--- a/registros_diarios/registros_ingreso_2025-07-10.xlsx
+++ b/registros_diarios/registros_ingreso_2025-07-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="28">
   <si>
     <t>DNI</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Resultado</t>
   </si>
   <si>
-    <t>39559614</t>
-  </si>
-  <si>
     <t>Cecilia Gimenez Ledesma</t>
   </si>
   <si>
@@ -97,13 +94,7 @@
     <t>FAP</t>
   </si>
   <si>
-    <t>1119424</t>
-  </si>
-  <si>
     <t>LAMY - EDDING</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>VERDE</t>
@@ -113,16 +104,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -138,7 +121,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -146,30 +129,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,28 +433,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -498,22 +463,22 @@
         <v>39559614</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>1119424</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,22 +486,22 @@
         <v>39559614</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>1119424</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -544,22 +509,22 @@
         <v>39559614</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>1119424</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -567,22 +532,22 @@
         <v>39559614</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>1119424</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -590,22 +555,22 @@
         <v>39559614</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>1119424</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -613,22 +578,22 @@
         <v>39559614</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>1119424</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -636,22 +601,22 @@
         <v>39559614</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>1119424</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -659,22 +624,22 @@
         <v>39559614</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9">
         <v>1119424</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -682,22 +647,22 @@
         <v>39559614</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10">
         <v>1119424</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -705,22 +670,22 @@
         <v>39559614</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>1119424</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -728,22 +693,22 @@
         <v>39559614</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12">
         <v>1119424</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -751,22 +716,22 @@
         <v>39559614</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13">
         <v>1119424</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -774,22 +739,22 @@
         <v>39559614</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14">
         <v>1119424</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -797,22 +762,22 @@
         <v>39559614</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15">
         <v>1119424</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -820,48 +785,45 @@
         <v>39559614</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16">
+        <v>1119424</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>39559614</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16">
-        <v>1119424</v>
-      </c>
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
       <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="E17">
+        <v>1119424</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
